--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T05:15:58+00:00</t>
+    <t>2026-10-01T16:35:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T16:35:47+00:00</t>
+    <t>2026-10-12T06:44:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:44:12+00:00</t>
+    <t>2026-10-12T07:51:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T07:51:03+00:00</t>
+    <t>2026-10-12T11:51:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T11:51:49+00:00</t>
+    <t>2026-10-21T14:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:48:12+00:00</t>
+    <t>2026-10-21T16:06:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -145,7 +145,7 @@
     <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_BirthOrder_CS#category</t>
   </si>
   <si>
-    <t>出生順呼称の区分。</t>
+    <t>出生順呼称の系列を分類する。son は長男・二男...の系列、daughter は長女・二女...の系列を示す。</t>
   </si>
   <si>
     <t>code</t>
@@ -157,7 +157,7 @@
     <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_BirthOrder_CS#order</t>
   </si>
   <si>
-    <t>区分内での順位。</t>
+    <t>系列内での順位（1を最年長とする）。</t>
   </si>
   <si>
     <t>integer</t>
@@ -304,7 +304,7 @@
     <t>unknown</t>
   </si>
   <si>
-    <t>詳細不明(text要素に詳細を記載)</t>
+    <t>詳細不明（text要素に詳細を記載）</t>
   </si>
 </sst>
 </file>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T16:06:49+00:00</t>
+    <t>2026-10-21T17:00:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T17:00:04+00:00</t>
+    <t>2026-10-29</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>FamilyMemberHistoryにおいて、家族内で用いられる出生順に基づく呼称（長男、二男、長女、二女など）を表現するためのCodeSystem。これらのコードは患者との続柄そのものではなく、FamilyMemberHistory.relationshipを補足する出生順の呼称を表す。</t>
+    <t>FamilyMemberHistoryにおいて、家族内で用いられる出生順に基づく呼称（長男、次男、長女、次女など）を表現するためのCodeSystem。これらのコードは患者との続柄そのものではなく、FamilyMemberHistory.relationshipを補足する出生順の呼称を表す。各コードには機械処理用のプロパティ（category：呼称系列、order：系列内順位）を付与しており、プログラムによる判定・集計に利用できる。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -145,7 +145,7 @@
     <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_BirthOrder_CS#category</t>
   </si>
   <si>
-    <t>出生順呼称の系列を分類する。son は長男・二男...の系列、daughter は長女・二女...の系列を示す。</t>
+    <t>son は男子に用いる呼称系列（長男・次男…）、daughter は女子に用いる呼称系列（長女・次女…）を表す。</t>
   </si>
   <si>
     <t>code</t>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="99">
   <si>
     <t>Property</t>
   </si>
@@ -187,6 +187,9 @@
     <t>second son</t>
   </si>
   <si>
+    <t>「次男」「二男」のいずれも使用可能である（戸籍の続柄欄では「二男」を使用）。</t>
+  </si>
+  <si>
     <t>son-3</t>
   </si>
   <si>
@@ -245,6 +248,9 @@
   </si>
   <si>
     <t>second daughter</t>
+  </si>
+  <si>
+    <t>「次女」「二女」のいずれも使用可能である（戸籍の続柄欄では「二女」を使用）。</t>
   </si>
   <si>
     <t>daughter-3</t>
@@ -707,17 +713,19 @@
       <c r="C3" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>52</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -726,10 +734,10 @@
         <v>52</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -738,10 +746,10 @@
         <v>52</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -750,10 +758,10 @@
         <v>52</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -762,10 +770,10 @@
         <v>52</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -774,10 +782,10 @@
         <v>52</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -786,10 +794,10 @@
         <v>52</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -798,10 +806,10 @@
         <v>52</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -810,10 +818,10 @@
         <v>52</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -822,22 +830,24 @@
         <v>52</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
         <v>52</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="2"/>
     </row>
@@ -846,10 +856,10 @@
         <v>52</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" s="2"/>
     </row>
@@ -858,10 +868,10 @@
         <v>52</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -870,10 +880,10 @@
         <v>52</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D17" s="2"/>
     </row>
@@ -882,10 +892,10 @@
         <v>52</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D18" s="2"/>
     </row>
@@ -894,10 +904,10 @@
         <v>52</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D19" s="2"/>
     </row>
@@ -906,10 +916,10 @@
         <v>52</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D20" s="2"/>
     </row>
@@ -918,10 +928,10 @@
         <v>52</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D21" s="2"/>
     </row>
@@ -930,13 +940,13 @@
         <v>52</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23">
@@ -944,13 +954,13 @@
         <v>52</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-birthorder-cs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="100">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29</t>
+    <t>2026-11-01</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,10 +85,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>FamilyMemberHistoryにおいて、家族内で用いられる出生順に基づく呼称（長男、次男、長女、次女など）を表現するためのCodeSystem。これらのコードは患者との続柄そのものではなく、FamilyMemberHistory.relationshipを補足する出生順の呼称を表す。各コードには機械処理用のプロパティ（category：呼称系列、order：系列内順位）を付与しており、プログラムによる判定・集計に利用できる。</t>
+    <t>JP Coreにて定義した家族歴のFamilyMemberHistoryリソースに関する家族内の出生順呼称コード</t>
   </si>
   <si>
     <t>Purpose</t>
+  </si>
+  <si>
+    <t>本コードシステムは、患者との続柄そのものを表すのではなく、FamilyMemberHistory.relationship を補足する情報として、家族内で用いられる出生順に基づく呼称を表現するために定義した。各コードには機械処理用のプロパティ（category：呼称系列、order：系列内順位）を付与しており、プログラムによる判定・集計に利用できる。</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -551,68 +554,70 @@
       <c r="A13" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -627,44 +632,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>22</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -679,288 +684,288 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
